--- a/tests/workbooktests/workbooks/test_ratehelpers.xlsx
+++ b/tests/workbooktests/workbooks/test_ratehelpers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FA925D-7657-474C-8E3F-5B2CA6174CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A781DBD-2244-465D-9026-F39DDB1B8E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60DEDABF-8191-4F74-809B-551F46E87618}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{60DEDABF-8191-4F74-809B-551F46E87618}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview Tabs" sheetId="18" r:id="rId1"/>
@@ -29,8 +29,10 @@
     <sheet name="MtMCrossCurrencyBasisSwapRateHe" sheetId="13" r:id="rId14"/>
     <sheet name="IborIborBasisSwapRateHelper" sheetId="14" r:id="rId15"/>
     <sheet name="OvernightIborBasisSwapRateHelpe" sheetId="15" r:id="rId16"/>
-    <sheet name="MultipleResetsSwapRateHelper" sheetId="16" r:id="rId17"/>
-    <sheet name="BMASwapRateHelper" sheetId="19" r:id="rId18"/>
+    <sheet name="OvernightOvernightBasisSwapRate" sheetId="20" r:id="rId17"/>
+    <sheet name="OvernightIndexedFundingRateHelp" sheetId="21" r:id="rId18"/>
+    <sheet name="MultipleResetsSwapRateHelper" sheetId="16" r:id="rId19"/>
+    <sheet name="BMASwapRateHelper" sheetId="19" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="262">
   <si>
     <t>tenor</t>
   </si>
@@ -735,6 +737,135 @@
   </si>
   <si>
     <t>Compound</t>
+  </si>
+  <si>
+    <t>float_convention</t>
+  </si>
+  <si>
+    <t>qlOvernightIndexFutureRateHelperFuture</t>
+  </si>
+  <si>
+    <t>qlBMASwapRateHelperSwap</t>
+  </si>
+  <si>
+    <t>qlBMASwapRateHelper</t>
+  </si>
+  <si>
+    <t>qlMultipleResetsSwapRateHelperSwap</t>
+  </si>
+  <si>
+    <t>float_index</t>
+  </si>
+  <si>
+    <t>collateral_curve</t>
+  </si>
+  <si>
+    <t>use_indexed_coupons</t>
+  </si>
+  <si>
+    <t>float_payment_frequency</t>
+  </si>
+  <si>
+    <t>float_stub_index_selection</t>
+  </si>
+  <si>
+    <t>2Y</t>
+  </si>
+  <si>
+    <t>30/360</t>
+  </si>
+  <si>
+    <t>semiannual</t>
+  </si>
+  <si>
+    <t>qlConstNotionalCrossCurrencySwapRateHelperSwap</t>
+  </si>
+  <si>
+    <t>payment_lag_on_notional_exchanges</t>
+  </si>
+  <si>
+    <t>base_stub_index_selection</t>
+  </si>
+  <si>
+    <t>quote_stub_index_selection</t>
+  </si>
+  <si>
+    <t>qlConstNotionalCrossCurrencyBasisSwapRateHelperSwap</t>
+  </si>
+  <si>
+    <t>fx_reset_fixing_days</t>
+  </si>
+  <si>
+    <t>fx_reset_fixing_calendar</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>qlMtMCrossCurrencyBasisSwapRateHelperSwap</t>
+  </si>
+  <si>
+    <t>qlMtMCrossCurrencyBasisSwapRateHelperFxResetFixingDays</t>
+  </si>
+  <si>
+    <t>qlMtMCrossCurrencyBasisSwapRateHelperFxResetFixingCalendar</t>
+  </si>
+  <si>
+    <t>overnight_payment_frequency</t>
+  </si>
+  <si>
+    <t>basis_on_ibor_leg</t>
+  </si>
+  <si>
+    <t>ibor_stub_index_selection</t>
+  </si>
+  <si>
+    <t>quarterly</t>
+  </si>
+  <si>
+    <t>Backward</t>
+  </si>
+  <si>
+    <t>base_index</t>
+  </si>
+  <si>
+    <t>other_index</t>
+  </si>
+  <si>
+    <t>discount_handle</t>
+  </si>
+  <si>
+    <t>base_averaging_method</t>
+  </si>
+  <si>
+    <t>other_averaging_method</t>
+  </si>
+  <si>
+    <t>qlOvernightOvernightBasisSwapRateHelper</t>
+  </si>
+  <si>
+    <t>qlOvernightOvernightBasisSwapRateHelperSwap</t>
+  </si>
+  <si>
+    <t>margin</t>
+  </si>
+  <si>
+    <t>overnight_index</t>
+  </si>
+  <si>
+    <t>payment_tenor</t>
+  </si>
+  <si>
+    <t>Act/360</t>
+  </si>
+  <si>
+    <t>qlOvernightIndexedFundingRateHelper</t>
+  </si>
+  <si>
+    <t>LastRelevantDate</t>
+  </si>
+  <si>
+    <t>qlOvernightIndexedFundingRateHelperSwap</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1135,10 +1266,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1154,9 +1310,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1194,7 +1350,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1300,7 +1456,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1451,99 +1607,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{340204E2-69E6-4DD5-97B8-ED1481D21F17}">
   <dimension ref="B1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="68" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" s="11" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="68" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>189</v>
       </c>
@@ -1555,16 +1711,16 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65244DF5-80D7-445B-8275-CBDDDF4E3506}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="3" width="93.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="2" max="3" width="93.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1572,16 +1728,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>33</v>
       </c>
@@ -1592,7 +1748,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>79</v>
       </c>
@@ -1603,7 +1759,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>80</v>
       </c>
@@ -1614,20 +1770,20 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="31" t="e">
-        <f ca="1">_xll.qlOvernightIndex("MyIndex",3,"EUR","TARGET","actual360")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C7" s="24" t="e">
-        <f ca="1">_xll.qlOvernightIndex("MyIndex",3,"EUR","TARGET","actual360")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="str">
+        <f>_xll.qlOvernightIndex("MyIndex",3,"EUR","TARGET","actual360",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R7C2OvernightIndex,H</v>
+      </c>
+      <c r="C7" s="24" t="str">
+        <f>_xll.qlOvernightIndex("MyIndex",3,"EUR","TARGET","actual360",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R7C3OvernightIndex,J</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>34</v>
       </c>
@@ -1638,7 +1794,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>109</v>
       </c>
@@ -1647,108 +1803,121 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="29" t="e">
-        <f ca="1">_xll.qlOvernightIndexFutureRateHelper(B4,B5,B6,B7,B8)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C10" s="20" t="e">
-        <f ca="1">_xll.qlOvernightIndexFutureRateHelper(C4,C5,C6,C7,C8,C9)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="29" t="str">
+        <f>_xll.qlOvernightIndexFutureRateHelper(B4,B5,B6,B7,B8)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R10C2OvernightIndexFutureRateHelper,A</v>
+      </c>
+      <c r="C10" s="20" t="str">
+        <f>_xll.qlOvernightIndexFutureRateHelper(C4,C5,C6,C7,C8,C9)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R10C3OvernightIndexFutureRateHelper,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C11" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C10)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="31">
+        <f>_xll.qlRateHelperQuote(B10)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C11" s="24">
+        <f>_xll.qlRateHelperQuote(C10)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C12" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C10)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="30">
+        <f>_xll.qlRateHelperLatestDate(B10)</f>
+        <v>45755</v>
+      </c>
+      <c r="C12" s="22">
+        <f>_xll.qlRateHelperLatestDate(C10)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C13" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C10)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B10)</f>
+        <v>45663</v>
+      </c>
+      <c r="C13" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C10)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C14" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C10)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B10)</f>
+        <v>45755</v>
+      </c>
+      <c r="C14" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C10)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C15" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C10)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B10)</f>
+        <v>45755</v>
+      </c>
+      <c r="C15" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C10)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C16" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C10)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="30">
+        <f>_xll.qlRateHelperPillarDate(B10)</f>
+        <v>45755</v>
+      </c>
+      <c r="C16" s="22">
+        <f>_xll.qlRateHelperPillarDate(C10)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="29" t="e">
-        <f ca="1">_xll.qlOvernightIndexFutureRateHelperConvexityAdjustment(B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C17" s="20" t="e">
-        <f ca="1">_xll.qlOvernightIndexFutureRateHelperConvexityAdjustment(C10)</f>
-        <v>#NAME?</v>
+      <c r="B17" s="29">
+        <f>_xll.qlOvernightIndexFutureRateHelperConvexityAdjustment(B10)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="20">
+        <f>_xll.qlOvernightIndexFutureRateHelperConvexityAdjustment(C10)</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" s="29" t="str" cm="1">
+        <f t="array" ref="B18">_xll.qlOvernightIndexFutureRateHelperFuture(B10)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R18C2OvernightIndexFuture,A</v>
+      </c>
+      <c r="C18" s="20" t="str" cm="1">
+        <f t="array" ref="C18">_xll.qlOvernightIndexFutureRateHelperFuture(C10)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R18C3OvernightIndexFuture,A</v>
       </c>
     </row>
   </sheetData>
@@ -1759,13 +1928,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBCB75F-B7E2-417A-B51A-9EA1B0672E67}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.7109375" customWidth="1"/>
-    <col min="2" max="2" width="70.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="49.6640625" customWidth="1"/>
+    <col min="2" max="2" width="70.33203125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1773,16 +1942,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>33</v>
       </c>
@@ -1790,7 +1959,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>84</v>
       </c>
@@ -1798,7 +1967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>85</v>
       </c>
@@ -1806,7 +1975,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>86</v>
       </c>
@@ -1814,73 +1983,73 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="24"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="20" t="e">
-        <f ca="1">_xll.qlSofrFutureRateHelper(B4,B5,B6,B7)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="20" t="str">
+        <f>_xll.qlSofrFutureRateHelper(B4,B5,B6,B7)</f>
+        <v>欣[test_ratehelpers.xlsx]SofrFutureRateHelper!R9C2SofrFutureRateHelper,A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B9)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="24">
+        <f>_xll.qlRateHelperQuote(B9)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B9)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="22">
+        <f>_xll.qlRateHelperLatestDate(B9)</f>
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B9)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="17">
+        <f>_xll.qlRateHelperEarliestDate(B9)</f>
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B9)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="22">
+        <f>_xll.qlRateHelperMaturityDate(B9)</f>
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B9)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(B9)</f>
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B9)</f>
-        <v>#NAME?</v>
+      <c r="B15" s="22">
+        <f>_xll.qlRateHelperPillarDate(B9)</f>
+        <v>45778</v>
       </c>
     </row>
   </sheetData>
@@ -1892,14 +2061,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B5DD58-D551-4EB6-8795-9A6336CDACCA}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.5703125" customWidth="1"/>
+    <col min="1" max="1" width="45.5546875" customWidth="1"/>
     <col min="2" max="2" width="105" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="105" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1907,16 +2076,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>88</v>
       </c>
@@ -1928,7 +2097,7 @@
       </c>
       <c r="D4" s="8"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
@@ -1940,7 +2109,7 @@
       </c>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>14</v>
       </c>
@@ -1952,21 +2121,21 @@
       </c>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="31" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C7" s="24" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
+      <c r="B7" s="31" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="24" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
       </c>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>81</v>
       </c>
@@ -1978,7 +2147,7 @@
       </c>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>2</v>
       </c>
@@ -1990,7 +2159,7 @@
       </c>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>63</v>
       </c>
@@ -2002,7 +2171,7 @@
       </c>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>89</v>
       </c>
@@ -2014,35 +2183,35 @@
       </c>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C12" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
+      <c r="B12" s="31" t="str">
+        <f>_xll.qlEuribor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R12C2Euribor,G</v>
+      </c>
+      <c r="C12" s="31" t="str">
+        <f>_xll.qlEuribor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R12C3Euribor,C</v>
       </c>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="31" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C13" s="24" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
+      <c r="B13" s="31" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R13C2YieldTermStructureHandle,H</v>
+      </c>
+      <c r="C13" s="31" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R13C3YieldTermStructureHandle,A</v>
       </c>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>91</v>
       </c>
@@ -2054,7 +2223,7 @@
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>100</v>
       </c>
@@ -2064,95 +2233,95 @@
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="29" t="e">
-        <f ca="1">_xll.qlConstNotionalCrossCurrencySwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C16" s="20" t="e">
-        <f ca="1">_xll.qlConstNotionalCrossCurrencySwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="29" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencySwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R16C2ConstNotionalCrossCurrencySwapRateHelper,A</v>
+      </c>
+      <c r="C16" s="20" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencySwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R16C3ConstNotionalCrossCurrencySwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C17" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C16)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="31">
+        <f>_xll.qlRateHelperQuote(B16)</f>
+        <v>0.04</v>
+      </c>
+      <c r="C17" s="24">
+        <f>_xll.qlRateHelperQuote(C16)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C18" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C16)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="30">
+        <f>_xll.qlRateHelperLatestDate(B16)</f>
+        <v>45846</v>
+      </c>
+      <c r="C18" s="22">
+        <f>_xll.qlRateHelperLatestDate(C16)</f>
+        <v>45847</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C19" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C16)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B16)</f>
+        <v>45665</v>
+      </c>
+      <c r="C19" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C16)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C16)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B16)</f>
+        <v>45846</v>
+      </c>
+      <c r="C20" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C16)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C21" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C16)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B16)</f>
+        <v>45846</v>
+      </c>
+      <c r="C21" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C16)</f>
+        <v>45847</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C22" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C16)</f>
-        <v>#NAME?</v>
+      <c r="B22" s="30">
+        <f>_xll.qlRateHelperPillarDate(B16)</f>
+        <v>45846</v>
+      </c>
+      <c r="C22" s="22">
+        <f>_xll.qlRateHelperPillarDate(C16)</f>
+        <v>45847</v>
       </c>
     </row>
   </sheetData>
@@ -2163,15 +2332,15 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE987B6-3AFC-4C21-983D-E8670E499AAD}">
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C48"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="108" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2179,16 +2348,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>93</v>
       </c>
@@ -2199,7 +2368,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
@@ -2210,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>14</v>
       </c>
@@ -2221,20 +2390,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="31" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C7" s="24" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="24" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>81</v>
       </c>
@@ -2245,7 +2414,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>2</v>
       </c>
@@ -2256,46 +2425,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C10" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="str">
+        <f>_xll.qlEuribor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R10C2Euribor,A</v>
+      </c>
+      <c r="C10" s="24" t="str">
+        <f>_xll.qlEuribor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R10C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C11" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="str">
+        <f>_xll.qlEuribor("6M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R11C2Euribor,A</v>
+      </c>
+      <c r="C11" s="24" t="str">
+        <f>_xll.qlEuribor("6M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R11C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="31" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C12" s="24" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R12C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C12" s="24" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R12C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>68</v>
       </c>
@@ -2306,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>94</v>
       </c>
@@ -2317,7 +2486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>95</v>
       </c>
@@ -2328,7 +2497,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>100</v>
       </c>
@@ -2337,7 +2506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>199</v>
       </c>
@@ -2346,95 +2515,334 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B18" s="31"/>
+      <c r="C18" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B19" s="31"/>
+      <c r="C19" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="24" t="str" cm="1">
+        <f t="array" ref="C20">_xll.qlStubIndexSelection(,,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R20C3StubIndexSelection,A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B21" s="31"/>
+      <c r="C21" s="24" t="str" cm="1">
+        <f t="array" ref="C21">_xll.qlStubIndexSelection(,,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R21C3StubIndexSelection,A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="29" t="e">
-        <f ca="1">_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14,B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C18" s="20" t="e">
-        <f ca="1">_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="B22" s="29" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14,B15)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R22C2ConstNotionalCrossCurrencyBasisSwapRateHelper,A</v>
+      </c>
+      <c r="C22" s="20" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R22C3ConstNotionalCrossCurrencyBasisSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B18)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C19" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C18)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="B23" s="31">
+        <f>_xll.qlRateHelperQuote(B22)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C23" s="24">
+        <f>_xll.qlRateHelperQuote(C22)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B18)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C18)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="B24" s="30">
+        <f>_xll.qlRateHelperLatestDate(B22)</f>
+        <v>45754</v>
+      </c>
+      <c r="C24" s="22">
+        <f>_xll.qlRateHelperLatestDate(C22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B18)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C21" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C18)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="B25" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B22)</f>
+        <v>45663</v>
+      </c>
+      <c r="C25" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C22)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B18)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C22" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C18)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="B26" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B22)</f>
+        <v>45754</v>
+      </c>
+      <c r="C26" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C22)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B18)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C23" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C18)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="B27" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B22)</f>
+        <v>45754</v>
+      </c>
+      <c r="C27" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B18)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C24" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C18)</f>
-        <v>#NAME?</v>
+      <c r="B28" s="30">
+        <f>_xll.qlRateHelperPillarDate(B22)</f>
+        <v>45754</v>
+      </c>
+      <c r="C28" s="22">
+        <f>_xll.qlRateHelperPillarDate(C22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="B29" s="30" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelperSwap(B22)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R29C2ConstNotionalCrossCurrencyBasisSwap,A</v>
+      </c>
+      <c r="C29" s="22" t="str">
+        <f>_xll.qlConstNotionalCrossCurrencyBasisSwapRateHelperSwap(C22)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R29C3ConstNotionalCrossCurrencyBasisSwap,A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="71">
+        <v>0.03</v>
+      </c>
+      <c r="C32" s="72">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="31">
+        <v>2</v>
+      </c>
+      <c r="C34" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="C37" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="74" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="75" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="73" t="s">
+        <v>224</v>
+      </c>
+      <c r="B40" s="31" t="str" cm="1">
+        <f t="array" ref="B40">_xll.qlEuribor("6m",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R40C2Euribor,A</v>
+      </c>
+      <c r="C40" s="24" t="str" cm="1">
+        <f t="array" ref="C40">_xll.qlEuribor("6m",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R40C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="73" t="s">
+        <v>225</v>
+      </c>
+      <c r="B41" s="31" t="str" cm="1">
+        <f t="array" ref="B41">_xll.qlFlatForward(B2,0.03,"Act/365")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R41C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C41" s="24" t="str" cm="1">
+        <f t="array" ref="C41">_xll.qlFlatForward(B2,0.03,"Act/365")</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R41C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="C42" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="31"/>
+      <c r="C43" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="73" t="s">
+        <v>226</v>
+      </c>
+      <c r="B44" s="31"/>
+      <c r="C44" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="73" t="s">
+        <v>227</v>
+      </c>
+      <c r="B45" s="31"/>
+      <c r="C45" s="24" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="73" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" s="31"/>
+      <c r="C46" s="24" t="str" cm="1">
+        <f t="array" ref="C46">_xll.qlStubIndexSelection(,,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R46C3StubIndexSelection,A</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="31" t="str" cm="1">
+        <f t="array" ref="B47">_xll.qlConstNotionalCrossCurrencySwapRateHelper(B32,B33,B34,B35,B36,B37,B38,B39,B40,B41,B42)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R47C2ConstNotionalCrossCurrencySwapRateHelper,A</v>
+      </c>
+      <c r="C47" s="24" t="str" cm="1">
+        <f t="array" ref="C47">_xll.qlConstNotionalCrossCurrencySwapRateHelper(C32,C33,C34,C35,C36,C37,C38,C39,C40,C41,C42,C43,C44,C45,C46)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R47C3ConstNotionalCrossCurrencySwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B48" s="29" t="str" cm="1">
+        <f t="array" ref="B48">_xll.qlConstNotionalCrossCurrencySwapRateHelperSwap(B47)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R48C2ConstNotionalCrossCurrencyFixedVsFloatingSwap,A</v>
+      </c>
+      <c r="C48" s="20" t="str" cm="1">
+        <f t="array" ref="C48">_xll.qlConstNotionalCrossCurrencySwapRateHelperSwap(C47)</f>
+        <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R48C3ConstNotionalCrossCurrencyFixedVsFloatingSwap,A</v>
       </c>
     </row>
   </sheetData>
@@ -2445,15 +2853,15 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD913001-8432-46A8-B805-3C8877FF8FEE}">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.28515625" customWidth="1"/>
-    <col min="2" max="2" width="100.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="108.28515625" customWidth="1"/>
+    <col min="1" max="1" width="44.33203125" customWidth="1"/>
+    <col min="2" max="2" width="100.88671875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="108.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2461,16 +2869,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>93</v>
       </c>
@@ -2481,7 +2889,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
@@ -2492,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>14</v>
       </c>
@@ -2503,20 +2911,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="31" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C7" s="24" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="24" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>81</v>
       </c>
@@ -2527,7 +2935,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>2</v>
       </c>
@@ -2538,46 +2946,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="31" t="e">
-        <f ca="1">_xll.qlCADLibor("6m")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C10" s="24" t="e">
-        <f ca="1">_xll.qlCADLibor("6m")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="str">
+        <f>_xll.qlCADLibor("6m",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R10C2CADLibor,A</v>
+      </c>
+      <c r="C10" s="31" t="str">
+        <f>_xll.qlCADLibor("6m",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R10C3CADLibor,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C11" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="str">
+        <f>_xll.qlEuribor("6M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R11C2Euribor,A</v>
+      </c>
+      <c r="C11" s="31" t="str">
+        <f>_xll.qlEuribor("6M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R11C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="31" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C12" s="24" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R12C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C12" s="31" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R12C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>97</v>
       </c>
@@ -2588,7 +2996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>94</v>
       </c>
@@ -2599,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>98</v>
       </c>
@@ -2610,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>99</v>
       </c>
@@ -2621,7 +3029,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>100</v>
       </c>
@@ -2630,7 +3038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>199</v>
       </c>
@@ -2639,95 +3047,177 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B19" s="31"/>
+      <c r="C19" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="24" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B21" s="31"/>
+      <c r="C21" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B22" s="31"/>
+      <c r="C22" s="24" t="str" cm="1">
+        <f t="array" ref="C22">_xll.qlStubIndexSelection(,,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R22C3StubIndexSelection,A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="24" t="str" cm="1">
+        <f t="array" ref="C23">_xll.qlStubIndexSelection(,,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R23C3StubIndexSelection,A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B19" s="29" t="e">
-        <f ca="1">_xll.qlMtMCrossCurrencyBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14,B15,B16)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C19" s="20" t="e">
-        <f ca="1">_xll.qlMtMCrossCurrencyBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="B24" s="29" t="str">
+        <f>_xll.qlMtMCrossCurrencyBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13,B14,B15,B16)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R24C2MtMCrossCurrencyBasisSwapRateHelper,A</v>
+      </c>
+      <c r="C24" s="20" t="str">
+        <f>_xll.qlMtMCrossCurrencyBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R24C3MtMCrossCurrencyBasisSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="B25" s="31">
+        <f>_xll.qlRateHelperQuote(B24)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C25" s="24">
+        <f>_xll.qlRateHelperQuote(C24)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C21" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="B26" s="30">
+        <f>_xll.qlRateHelperLatestDate(B24)</f>
+        <v>45757</v>
+      </c>
+      <c r="C26" s="22">
+        <f>_xll.qlRateHelperLatestDate(C24)</f>
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C22" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="B27" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B24)</f>
+        <v>45667</v>
+      </c>
+      <c r="C27" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C24)</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C23" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="B28" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B24)</f>
+        <v>45757</v>
+      </c>
+      <c r="C28" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C24)</f>
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C24" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="B29" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B24)</f>
+        <v>45757</v>
+      </c>
+      <c r="C29" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C24)</f>
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C25" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C19)</f>
-        <v>#NAME?</v>
+      <c r="B30" s="30">
+        <f>_xll.qlRateHelperPillarDate(B24)</f>
+        <v>45757</v>
+      </c>
+      <c r="C30" s="22">
+        <f>_xll.qlRateHelperPillarDate(C24)</f>
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="B31" s="8" cm="1">
+        <f t="array" ref="B31">_xll.qlMtMCrossCurrencyBasisSwapRateHelperFxResetFixingDays(B24)</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="8" cm="1">
+        <f t="array" ref="C31">_xll.qlMtMCrossCurrencyBasisSwapRateHelperFxResetFixingDays(C24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C32" s="8" t="str" cm="1">
+        <f t="array" ref="C32">_xll.qlMtMCrossCurrencyBasisSwapRateHelperFxResetFixingCalendar(C24)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B33" s="8" t="str">
+        <f>_xll.qlMtMCrossCurrencyBasisSwapRateHelperSwap(B24)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R33C2MtMCrossCurrencyBasisSwap,A</v>
+      </c>
+      <c r="C33" s="8" t="str">
+        <f>_xll.qlMtMCrossCurrencyBasisSwapRateHelperSwap(C24)</f>
+        <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R33C3MtMCrossCurrencyBasisSwap,A</v>
       </c>
     </row>
   </sheetData>
@@ -2739,13 +3229,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96BD365-E285-4A84-8EB5-437F3B693A20}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.5703125" customWidth="1"/>
-    <col min="2" max="2" width="89.140625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="45.5546875" customWidth="1"/>
+    <col min="2" max="2" width="89.109375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2753,16 +3243,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>93</v>
       </c>
@@ -2770,7 +3260,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
@@ -2778,7 +3268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>47</v>
       </c>
@@ -2786,16 +3276,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="24" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="24" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>81</v>
       </c>
@@ -2803,7 +3293,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>2</v>
       </c>
@@ -2811,34 +3301,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="24" t="str">
+        <f>_xll.qlEuribor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R10C2Euribor,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="24" t="e">
-        <f ca="1">_xll.qlAUDLibor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="24" t="str">
+        <f>_xll.qlAUDLibor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R11C2AUDLibor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="24" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="24" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R12C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>102</v>
       </c>
@@ -2846,76 +3336,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="20" t="e">
-        <f ca="1">_xll.qlIborIborBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="str">
+        <f>_xll.qlIborIborBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13)</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R14C2IborIborBasisSwapRateHelper,D</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="24">
+        <f>_xll.qlRateHelperQuote(B14)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="22">
+        <f>_xll.qlRateHelperLatestDate(B14)</f>
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="17">
+        <f>_xll.qlRateHelperEarliestDate(B14)</f>
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="22">
+        <f>_xll.qlRateHelperMaturityDate(B14)</f>
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(B14)</f>
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="22">
+        <f>_xll.qlRateHelperPillarDate(B14)</f>
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="20" t="e">
-        <f ca="1">_xll.qlIborIborBasisSwapRateHelperSwap(B14)</f>
-        <v>#NAME?</v>
+      <c r="B21" s="20" t="str">
+        <f>_xll.qlIborIborBasisSwapRateHelperSwap(B14)</f>
+        <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R21C2Swap,A</v>
       </c>
     </row>
   </sheetData>
@@ -2926,14 +3416,15 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4B8905-8681-4349-B601-E6FC9C6EE563}">
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.85546875" customWidth="1"/>
+    <col min="1" max="1" width="44.88671875" customWidth="1"/>
     <col min="2" max="2" width="94" style="8" customWidth="1"/>
+    <col min="3" max="3" width="85.77734375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2941,161 +3432,306 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>93</v>
       </c>
       <c r="B4" s="57">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="57">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="24">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="24" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="24" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="24" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>81</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="24" t="e">
-        <f ca="1">_xll.qlSofr()</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="24" t="str">
+        <f>_xll.qlSofr(,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R10C2Sofr,A</v>
+      </c>
+      <c r="C10" s="24" t="str">
+        <f>_xll.qlSofr(,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R10C3Sofr,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="24" t="e">
-        <f ca="1">_xll.qlAUDLibor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="24" t="str">
+        <f>_xll.qlAUDLibor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R11C2AUDLibor,A</v>
+      </c>
+      <c r="C11" s="24" t="str">
+        <f>_xll.qlAUDLibor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R11C3AUDLibor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="24" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="B12" s="24" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R12C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C12" s="24" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R12C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B20" s="24"/>
+      <c r="C20" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="8" t="str" cm="1">
+        <f t="array" ref="C21">_xll.qlStubIndexSelection(,,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R21C3StubIndexSelection,A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="20" t="e">
-        <f ca="1">_xll.qlOvernightIborBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+      <c r="B22" s="20" t="str">
+        <f>_xll.qlOvernightIborBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R22C2OvernightIborBasisSwapRateHelper,A</v>
+      </c>
+      <c r="C22" s="20" t="str">
+        <f>_xll.qlOvernightIborBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R22C3OvernightIborBasisSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="B23" s="24">
+        <f>_xll.qlRateHelperQuote(B22)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C23" s="24">
+        <f>_xll.qlRateHelperQuote(C22)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="B24" s="22">
+        <f>_xll.qlRateHelperLatestDate(B22)</f>
+        <v>45755</v>
+      </c>
+      <c r="C24" s="22">
+        <f>_xll.qlRateHelperLatestDate(C22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="B25" s="17">
+        <f>_xll.qlRateHelperEarliestDate(B22)</f>
+        <v>45665</v>
+      </c>
+      <c r="C25" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C22)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+      <c r="B26" s="22">
+        <f>_xll.qlRateHelperMaturityDate(B22)</f>
+        <v>45755</v>
+      </c>
+      <c r="C26" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="B27" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(B22)</f>
+        <v>45755</v>
+      </c>
+      <c r="C27" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="B28" s="22">
+        <f>_xll.qlRateHelperPillarDate(B22)</f>
+        <v>45755</v>
+      </c>
+      <c r="C28" s="22">
+        <f>_xll.qlRateHelperPillarDate(C22)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="20" t="e">
-        <f ca="1">_xll.qlOvernightIborBasisSwapRateHelperSwap(B13)</f>
-        <v>#NAME?</v>
+      <c r="B29" s="20" t="str">
+        <f>_xll.qlOvernightIborBasisSwapRateHelperSwap(B22)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R29C2Swap,A</v>
+      </c>
+      <c r="C29" s="20" t="str">
+        <f>_xll.qlOvernightIborBasisSwapRateHelperSwap(C22)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R29C3Swap,A</v>
       </c>
     </row>
   </sheetData>
@@ -3104,32 +3740,439 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DACB900-6F87-43DE-88E1-BD91076BD096}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC158AE0-709A-4B53-939D-44DED3DE1063}">
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" customWidth="1"/>
-    <col min="2" max="3" width="89.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.21875" customWidth="1"/>
+    <col min="2" max="2" width="65.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="58.77734375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="7">
         <v>45663</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="78">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C4" s="78">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="8">
+        <v>2</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B10" s="8" t="str" cm="1">
+        <f t="array" ref="B10">_xll.qlEstr(,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R10C2Estr,G</v>
+      </c>
+      <c r="C10" s="8" t="str" cm="1">
+        <f t="array" ref="C10">_xll.qlEstr(,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R10C3Estr,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="8" t="str" cm="1">
+        <f t="array" ref="B11">_xll.qlEonia(,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R11C2Eonia,I</v>
+      </c>
+      <c r="C11" s="8" t="str" cm="1">
+        <f t="array" ref="C11">_xll.qlEonia(,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R11C3Eonia,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="8" t="str" cm="1">
+        <f t="array" ref="C12">_xll.qlFlatForward(B2,0.03,"Act/365")</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R12C3YieldTermStructureHandle,E</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="8" t="str" cm="1">
+        <f t="array" ref="B19">_xll.qlOvernightOvernightBasisSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R19C2OvernightOvernightBasisSwapRateHelper,A</v>
+      </c>
+      <c r="C19" s="8" t="str" cm="1">
+        <f t="array" ref="C19">_xll.qlOvernightOvernightBasisSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R19C3OvernightOvernightBasisSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" s="8" t="str" cm="1">
+        <f t="array" ref="B20">_xll.qlOvernightOvernightBasisSwapRateHelperSwap(B19)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R20C2Swap,A</v>
+      </c>
+      <c r="C20" s="8" t="str" cm="1">
+        <f t="array" ref="C20">_xll.qlOvernightOvernightBasisSwapRateHelperSwap(C19)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightOvernightBasisSwapRate!R20C3Swap,A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19342C27-3098-4675-9315-17F55D243248}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="96.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="96.21875" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="7">
+        <v>45663</v>
+      </c>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="78">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C4" s="78">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="8" t="str" cm="1">
+        <f t="array" ref="B10">_xll.qlEstr(_xll.qlFlatForward(B2,0.03,"Act/365"),B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIndexedFundingRateHelp!R10C2Estr,A</v>
+      </c>
+      <c r="C10" s="8" t="str" cm="1">
+        <f t="array" ref="C10">_xll.qlEstr(_xll.qlFlatForward(B2,0.03,"Act/365"),B2)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIndexedFundingRateHelp!R10C3Estr,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B18" s="8" t="str" cm="1">
+        <f t="array" ref="B18">_xll.qlOvernightIndexedFundingRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIndexedFundingRateHelp!R18C2OvernightIndexedFundingRateHelper,A</v>
+      </c>
+      <c r="C18" s="8" t="str" cm="1">
+        <f t="array" ref="C18">_xll.qlOvernightIndexedFundingRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIndexedFundingRateHelp!R18C3OvernightIndexedFundingRateHelper,A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="8" t="str" cm="1">
+        <f t="array" ref="B19">_xll.qlOvernightIndexedFundingRateHelperSwap(B18)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIndexedFundingRateHelp!R19C2Swap,A</v>
+      </c>
+      <c r="C19" s="8" t="str" cm="1">
+        <f t="array" ref="C19">_xll.qlOvernightIndexedFundingRateHelperSwap(C18)</f>
+        <v>欣[test_ratehelpers.xlsx]OvernightIndexedFundingRateHelp!R19C3Swap,A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DACB900-6F87-43DE-88E1-BD91076BD096}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.6640625" customWidth="1"/>
+    <col min="2" max="3" width="89.6640625" style="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="7">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>47</v>
       </c>
@@ -3140,7 +4183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>107</v>
       </c>
@@ -3151,7 +4194,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>88</v>
       </c>
@@ -3162,20 +4205,20 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="31" t="e">
-        <f ca="1">_xll.qlUSDLibor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C7" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="str">
+        <f>_xll.qlUSDLibor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R7C2USDLibor,G</v>
+      </c>
+      <c r="C7" s="24" t="str">
+        <f>_xll.qlEuribor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R7C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>108</v>
       </c>
@@ -3186,17 +4229,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>46</v>
       </c>
       <c r="B9" s="31"/>
-      <c r="C9" s="24" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="24" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R9C3YieldTermStructureHandle,J</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>109</v>
       </c>
@@ -3205,7 +4248,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>45</v>
       </c>
@@ -3214,7 +4257,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="69" t="s">
         <v>63</v>
       </c>
@@ -3225,7 +4268,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>89</v>
       </c>
@@ -3234,7 +4277,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>110</v>
       </c>
@@ -3243,95 +4286,108 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="B15" s="38" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlMultipleResetsSwapRateHelper(B4,B5,B6,B7,B8,,,,B12)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C15" s="39" t="e" cm="1">
-        <f t="array" aca="1" ref="C15" ca="1">_xll.qlMultipleResetsSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="38" t="str" cm="1">
+        <f t="array" ref="B15">_xll.qlMultipleResetsSwapRateHelper(B4,B5,B6,B7,B8,,,,B12)</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R15C2MultipleResetsSwapRateHelper,A</v>
+      </c>
+      <c r="C15" s="39" t="str" cm="1">
+        <f t="array" ref="C15">_xll.qlMultipleResetsSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12)</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R15C3MultipleResetsSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C16" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="31">
+        <f>_xll.qlRateHelperQuote(B15)</f>
+        <v>0.3</v>
+      </c>
+      <c r="C16" s="24">
+        <f>_xll.qlRateHelperQuote(C15)</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C17" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="30">
+        <f>_xll.qlRateHelperLatestDate(B15)</f>
+        <v>46030</v>
+      </c>
+      <c r="C17" s="22">
+        <f>_xll.qlRateHelperLatestDate(C15)</f>
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C18" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B15)</f>
+        <v>45665</v>
+      </c>
+      <c r="C18" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C15)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C19" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B15)</f>
+        <v>46030</v>
+      </c>
+      <c r="C19" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C15)</f>
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B15)</f>
+        <v>46030</v>
+      </c>
+      <c r="C20" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C15)</f>
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C21" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C15)</f>
-        <v>#NAME?</v>
+      <c r="B21" s="30">
+        <f>_xll.qlRateHelperPillarDate(B15)</f>
+        <v>46030</v>
+      </c>
+      <c r="C21" s="22">
+        <f>_xll.qlRateHelperPillarDate(C15)</f>
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="30" t="str" cm="1">
+        <f t="array" ref="B22">_xll.qlMultipleResetsSwapRateHelperSwap(B15)</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R22C2MultipleResetsSwap,A</v>
+      </c>
+      <c r="C22" s="22" t="str" cm="1">
+        <f t="array" ref="C22">_xll.qlMultipleResetsSwapRateHelperSwap(C15)</f>
+        <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R22C3MultipleResetsSwap,A</v>
       </c>
     </row>
   </sheetData>
@@ -3339,190 +4395,331 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F59CF0C-0921-460E-B694-8716C5AC312E}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA980392-DB4E-4511-92AD-9631BAA7D1FD}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.6640625" customWidth="1"/>
+    <col min="2" max="2" width="73.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="7">
+      <c r="B1" s="1">
         <v>45663</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="B4" s="43">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="46">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="15">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="46" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlBMAIndex()</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+      <c r="B9" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="20" t="str">
+        <f>_xll.qlDepositRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R11C2DepositRateHelper,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="24">
+        <f>_xll.qlRateHelperQuote(B11)</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="22">
+        <f>_xll.qlRateHelperLatestDate(B11)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="17">
+        <f>_xll.qlRateHelperEarliestDate(B11)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="22">
+        <f>_xll.qlRateHelperMaturityDate(B11)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(B11)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="22">
+        <f>_xll.qlRateHelperPillarDate(B11)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15">
+        <v>0.02</v>
+      </c>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="46" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlUSDLibor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="46" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="20" t="e" cm="1">
-        <f t="array" aca="1" ref="B14" ca="1">_xll.qlBMASwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+      <c r="B20" s="24" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R20C2Euribor,A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="20" t="str">
+        <f>_xll.qlDepositRateHelper2(B19,B20)</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R21C2DepositRateHelper,A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="B22" s="24">
+        <f>_xll.qlRateHelperQuote(B21)</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+      <c r="B23" s="22">
+        <f>_xll.qlRateHelperLatestDate(B21)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="B24" s="17">
+        <f>_xll.qlRateHelperEarliestDate(B21)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="B25" s="22">
+        <f>_xll.qlRateHelperMaturityDate(B21)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="B26" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(B21)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
+      <c r="B27" s="22">
+        <f>_xll.qlRateHelperPillarDate(B21)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="8"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="15">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="17">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="24" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R31C2Euribor,A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="20" t="str">
+        <f>_xll.qlDepositRateHelper3(B29,B30,B31)</f>
+        <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R32C2DepositRateHelper,A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="24">
+        <f>_xll.qlRateHelperQuote(B32)</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="22">
+        <f>_xll.qlRateHelperLatestDate(B32)</f>
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="17">
+        <f>_xll.qlRateHelperEarliestDate(B32)</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="22">
+        <f>_xll.qlRateHelperMaturityDate(B32)</f>
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(B32)</f>
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="22">
+        <f>_xll.qlRateHelperPillarDate(B32)</f>
+        <v>45757</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3530,331 +4727,199 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA980392-DB4E-4511-92AD-9631BAA7D1FD}">
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F59CF0C-0921-460E-B694-8716C5AC312E}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="1"/>
-    <col min="2" max="2" width="73.7109375" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.33203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="7">
         <v>45663</v>
       </c>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="1" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="15">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="43">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="46" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="20" t="e">
-        <f ca="1">_xll.qlDepositRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="46" t="str" cm="1">
+        <f t="array" ref="B11">_xll.qlBMAIndex(,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]BMASwapRateHelper!R11C2BMAIndex,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="46" t="str" cm="1">
+        <f t="array" ref="B12">_xll.qlUSDLibor("3M",,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]BMASwapRateHelper!R12C2USDLibor,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="46" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]BMASwapRateHelper!R13C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="20" t="str" cm="1">
+        <f t="array" ref="B14">_xll.qlBMASwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12,B13)</f>
+        <v>欣[test_ratehelpers.xlsx]BMASwapRateHelper!R14C2BMASwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B11)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="B15" s="24">
+        <f>_xll.qlRateHelperQuote(B14)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B11)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+      <c r="B16" s="22">
+        <f>_xll.qlRateHelperLatestDate(B14)</f>
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B11)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="B17" s="17">
+        <f>_xll.qlRateHelperEarliestDate(B14)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B11)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="B18" s="22">
+        <f>_xll.qlRateHelperMaturityDate(B14)</f>
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B11)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="B19" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(B14)</f>
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B11)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="15">
-        <v>0.02</v>
-      </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="20" t="e">
-        <f ca="1">_xll.qlDepositRateHelper2(B19,B20)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B21)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B21)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B21)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B21)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B21)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B21)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="15">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="17">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="20" t="e">
-        <f ca="1">_xll.qlDepositRateHelper3(B29,B30,B31)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B32)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B32)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B32)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B32)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B32)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B32)</f>
-        <v>#NAME?</v>
-      </c>
+      <c r="B20" s="22">
+        <f>_xll.qlRateHelperPillarDate(B14)</f>
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" s="22" t="str" cm="1">
+        <f t="array" ref="B21">_xll.qlBMASwapRateHelperSwap(B14)</f>
+        <v>欣[test_ratehelpers.xlsx]BMASwapRateHelper!R21C2BMASwap,A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3865,13 +4930,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC39AE1-3C8B-4BAC-BB4F-63180FABE33E}">
   <dimension ref="A1:G64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="4" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="58.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -3880,21 +4945,21 @@
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="1" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>18</v>
       </c>
@@ -3908,7 +4973,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>19</v>
       </c>
@@ -3922,7 +4987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>20</v>
       </c>
@@ -3936,7 +5001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>14</v>
       </c>
@@ -3950,24 +5015,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C8" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D8" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C8" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D8" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>22</v>
       </c>
@@ -3981,7 +5046,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>2</v>
       </c>
@@ -3995,7 +5060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>3</v>
       </c>
@@ -4009,7 +5074,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>37</v>
       </c>
@@ -4021,7 +5086,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>38</v>
       </c>
@@ -4033,7 +5098,7 @@
         <v>45816</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>39</v>
       </c>
@@ -4045,131 +5110,131 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="29" t="e">
-        <f ca="1">_xll.qlFRARateHelper(B4,B5,B6,B7,B8,B9,B10,B11,,,,B2)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C15" s="29" t="e">
-        <f ca="1">_xll.qlFRARateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,B2)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D15" s="20" t="e">
-        <f ca="1">_xll.qlFRARateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,B2)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="29" t="str">
+        <f>_xll.qlFRARateHelper(B4,B5,B6,B7,B8,B9,B10,B11,,,,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R15C2FraRateHelper,A</v>
+      </c>
+      <c r="C15" s="29" t="str">
+        <f>_xll.qlFRARateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R15C3FraRateHelper,A</v>
+      </c>
+      <c r="D15" s="20" t="str">
+        <f>_xll.qlFRARateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,B2)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R15C4FraRateHelper,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C16" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D16" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="31">
+        <f>_xll.qlRateHelperQuote(B15)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C16" s="31">
+        <f>_xll.qlRateHelperQuote(C15)</f>
+        <v>95.5</v>
+      </c>
+      <c r="D16" s="24">
+        <f>_xll.qlRateHelperQuote(D15)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C17" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D17" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="30">
+        <f>_xll.qlRateHelperLatestDate(B15)</f>
+        <v>45846</v>
+      </c>
+      <c r="C17" s="30">
+        <f>_xll.qlRateHelperLatestDate(C15)</f>
+        <v>45816</v>
+      </c>
+      <c r="D17" s="22">
+        <f>_xll.qlRateHelperLatestDate(D15)</f>
+        <v>45816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C18" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D18" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B15)</f>
+        <v>45665</v>
+      </c>
+      <c r="C18" s="28">
+        <f>_xll.qlRateHelperEarliestDate(C15)</f>
+        <v>45663</v>
+      </c>
+      <c r="D18" s="17">
+        <f>_xll.qlRateHelperEarliestDate(D15)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C19" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D19" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B15)</f>
+        <v>45846</v>
+      </c>
+      <c r="C19" s="30">
+        <f>_xll.qlRateHelperMaturityDate(C15)</f>
+        <v>45845</v>
+      </c>
+      <c r="D19" s="22">
+        <f>_xll.qlRateHelperMaturityDate(D15)</f>
+        <v>45845</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D20" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B15)</f>
+        <v>45846</v>
+      </c>
+      <c r="C20" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(C15)</f>
+        <v>45845</v>
+      </c>
+      <c r="D20" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(D15)</f>
+        <v>45845</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C21" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D21" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D15)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="30">
+        <f>_xll.qlRateHelperPillarDate(B15)</f>
+        <v>45846</v>
+      </c>
+      <c r="C21" s="30">
+        <f>_xll.qlRateHelperPillarDate(C15)</f>
+        <v>45816</v>
+      </c>
+      <c r="D21" s="22">
+        <f>_xll.qlRateHelperPillarDate(D15)</f>
+        <v>45816</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
         <v>18</v>
       </c>
@@ -4183,7 +5248,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>19</v>
       </c>
@@ -4197,24 +5262,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C25" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D25" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="31" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R25C2Euribor,A</v>
+      </c>
+      <c r="C25" s="31" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R25C3Euribor,A</v>
+      </c>
+      <c r="D25" s="24" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R25C4Euribor,A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>37</v>
       </c>
@@ -4226,7 +5291,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>38</v>
       </c>
@@ -4236,7 +5301,7 @@
         <v>45724</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>39</v>
       </c>
@@ -4248,131 +5313,131 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="29" t="e">
-        <f ca="1">_xll.qlFRARateHelper2(B23,B24,B25)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C29" s="29" t="e">
-        <f ca="1">_xll.qlFRARateHelper2(C23,C24,C25,C26,,C28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D29" s="20" t="e">
-        <f ca="1">_xll.qlFRARateHelper2(D23,D24,D25,D26,D27,D28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="29" t="str">
+        <f>_xll.qlFRARateHelper2(B23,B24,B25)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R29C2FraRateHelper,A</v>
+      </c>
+      <c r="C29" s="29" t="str">
+        <f>_xll.qlFRARateHelper2(C23,C24,C25,C26,,C28)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R29C3FraRateHelper,A</v>
+      </c>
+      <c r="D29" s="20" t="str">
+        <f>_xll.qlFRARateHelper2(D23,D24,D25,D26,D27,D28)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R29C4FraRateHelper,A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C30" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D30" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="31">
+        <f>_xll.qlRateHelperQuote(B29)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C30" s="31">
+        <f>_xll.qlRateHelperQuote(C29)</f>
+        <v>95.5</v>
+      </c>
+      <c r="D30" s="24">
+        <f>_xll.qlRateHelperQuote(D29)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C31" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D31" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="30">
+        <f>_xll.qlRateHelperLatestDate(B29)</f>
+        <v>45755</v>
+      </c>
+      <c r="C31" s="30">
+        <f>_xll.qlRateHelperLatestDate(C29)</f>
+        <v>45755</v>
+      </c>
+      <c r="D31" s="22">
+        <f>_xll.qlRateHelperLatestDate(D29)</f>
+        <v>45724</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C32" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D32" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B29)</f>
+        <v>45665</v>
+      </c>
+      <c r="C32" s="28">
+        <f>_xll.qlRateHelperEarliestDate(C29)</f>
+        <v>45665</v>
+      </c>
+      <c r="D32" s="17">
+        <f>_xll.qlRateHelperEarliestDate(D29)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C33" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D33" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B29)</f>
+        <v>45755</v>
+      </c>
+      <c r="C33" s="30">
+        <f>_xll.qlRateHelperMaturityDate(C29)</f>
+        <v>45755</v>
+      </c>
+      <c r="D33" s="22">
+        <f>_xll.qlRateHelperMaturityDate(D29)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C34" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D34" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B29)</f>
+        <v>45755</v>
+      </c>
+      <c r="C34" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(C29)</f>
+        <v>45755</v>
+      </c>
+      <c r="D34" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(D29)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C35" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D35" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="30">
+        <f>_xll.qlRateHelperPillarDate(B29)</f>
+        <v>45755</v>
+      </c>
+      <c r="C35" s="30">
+        <f>_xll.qlRateHelperPillarDate(C29)</f>
+        <v>45755</v>
+      </c>
+      <c r="D35" s="22">
+        <f>_xll.qlRateHelperPillarDate(D29)</f>
+        <v>45724</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
         <v>18</v>
       </c>
@@ -4386,7 +5451,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>27</v>
       </c>
@@ -4400,7 +5465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="33" t="s">
         <v>28</v>
       </c>
@@ -4414,24 +5479,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C40" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D40" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="31" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R40C2Euribor,A</v>
+      </c>
+      <c r="C40" s="31" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R40C3Euribor,A</v>
+      </c>
+      <c r="D40" s="24" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R40C4Euribor,A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="33" t="s">
         <v>37</v>
       </c>
@@ -4443,7 +5508,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
         <v>38</v>
       </c>
@@ -4453,7 +5518,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>39</v>
       </c>
@@ -4465,131 +5530,131 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="29" t="e">
-        <f ca="1">_xll.qlFRARateHelper3(B37,B38,B39,B40)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C44" s="29" t="e">
-        <f ca="1">_xll.qlFRARateHelper3(C37,C38,C39,C40,C41,,C43)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D44" s="20" t="e">
-        <f ca="1">_xll.qlFRARateHelper3(D37,D38,D39,D40,D41,D42,D43)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="29" t="str">
+        <f>_xll.qlFRARateHelper3(B37,B38,B39,B40)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R44C2FraRateHelper,A</v>
+      </c>
+      <c r="C44" s="29" t="str">
+        <f>_xll.qlFRARateHelper3(C37,C38,C39,C40,C41,,C43)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R44C3FraRateHelper,A</v>
+      </c>
+      <c r="D44" s="20" t="str">
+        <f>_xll.qlFRARateHelper3(D37,D38,D39,D40,D41,D42,D43)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R44C4FraRateHelper,A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C45" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D45" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D44)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="31">
+        <f>_xll.qlRateHelperQuote(B44)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C45" s="31">
+        <f>_xll.qlRateHelperQuote(C44)</f>
+        <v>95.5</v>
+      </c>
+      <c r="D45" s="24">
+        <f>_xll.qlRateHelperQuote(D44)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C46" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D46" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D44)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="30">
+        <f>_xll.qlRateHelperLatestDate(B44)</f>
+        <v>45918</v>
+      </c>
+      <c r="C46" s="30">
+        <f>_xll.qlRateHelperLatestDate(C44)</f>
+        <v>45917</v>
+      </c>
+      <c r="D46" s="22">
+        <f>_xll.qlRateHelperLatestDate(D44)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C47" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D47" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D44)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B44)</f>
+        <v>45826</v>
+      </c>
+      <c r="C47" s="28">
+        <f>_xll.qlRateHelperEarliestDate(C44)</f>
+        <v>45826</v>
+      </c>
+      <c r="D47" s="17">
+        <f>_xll.qlRateHelperEarliestDate(D44)</f>
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B48" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C48" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D48" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D44)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B44)</f>
+        <v>45917</v>
+      </c>
+      <c r="C48" s="30">
+        <f>_xll.qlRateHelperMaturityDate(C44)</f>
+        <v>45917</v>
+      </c>
+      <c r="D48" s="22">
+        <f>_xll.qlRateHelperMaturityDate(D44)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B49" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C49" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D49" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D44)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B44)</f>
+        <v>45918</v>
+      </c>
+      <c r="C49" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(C44)</f>
+        <v>45918</v>
+      </c>
+      <c r="D49" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(D44)</f>
+        <v>45918</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C50" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C44)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D50" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D44)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="30">
+        <f>_xll.qlRateHelperPillarDate(B44)</f>
+        <v>45918</v>
+      </c>
+      <c r="C50" s="30">
+        <f>_xll.qlRateHelperPillarDate(C44)</f>
+        <v>45917</v>
+      </c>
+      <c r="D50" s="22">
+        <f>_xll.qlRateHelperPillarDate(D44)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="32" t="s">
         <v>18</v>
       </c>
@@ -4603,7 +5668,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="16" t="s">
         <v>30</v>
       </c>
@@ -4617,24 +5682,24 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C54" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D54" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="31" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R54C2Euribor,A</v>
+      </c>
+      <c r="C54" s="31" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R54C3Euribor,A</v>
+      </c>
+      <c r="D54" s="24" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R54C4Euribor,A</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="33" t="s">
         <v>37</v>
       </c>
@@ -4646,7 +5711,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="33" t="s">
         <v>38</v>
       </c>
@@ -4656,7 +5721,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="33" t="s">
         <v>39</v>
       </c>
@@ -4668,123 +5733,123 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B58" s="29" t="e">
-        <f ca="1">_xll.qlFRARateHelper4(B52,B53,B54)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C58" s="29" t="e">
-        <f ca="1">_xll.qlFRARateHelper4(C52,C53,C54,C55,,C57)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D58" s="20" t="e">
-        <f ca="1">_xll.qlFRARateHelper4(D52,D53,D54,D55,D56,D57)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B58" s="29" t="str">
+        <f>_xll.qlFRARateHelper4(B52,B53,B54)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R58C2FraRateHelper,A</v>
+      </c>
+      <c r="C58" s="29" t="str">
+        <f>_xll.qlFRARateHelper4(C52,C53,C54,C55,,C57)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R58C3FraRateHelper,A</v>
+      </c>
+      <c r="D58" s="20" t="str">
+        <f>_xll.qlFRARateHelper4(D52,D53,D54,D55,D56,D57)</f>
+        <v>欣[test_ratehelpers.xlsx]FRARateHelper!R58C4FraRateHelper,A</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C59" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D59" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D58)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B59" s="31">
+        <f>_xll.qlRateHelperQuote(B58)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C59" s="31">
+        <f>_xll.qlRateHelperQuote(C58)</f>
+        <v>95.5</v>
+      </c>
+      <c r="D59" s="24">
+        <f>_xll.qlRateHelperQuote(D58)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B60" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C60" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D60" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D58)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B60" s="30">
+        <f>_xll.qlRateHelperLatestDate(B58)</f>
+        <v>45938</v>
+      </c>
+      <c r="C60" s="30">
+        <f>_xll.qlRateHelperLatestDate(C58)</f>
+        <v>45938</v>
+      </c>
+      <c r="D60" s="22">
+        <f>_xll.qlRateHelperLatestDate(D58)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C61" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D61" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D58)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B61" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B58)</f>
+        <v>45846</v>
+      </c>
+      <c r="C61" s="28">
+        <f>_xll.qlRateHelperEarliestDate(C58)</f>
+        <v>45846</v>
+      </c>
+      <c r="D61" s="17">
+        <f>_xll.qlRateHelperEarliestDate(D58)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C62" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D62" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D58)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B62" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B58)</f>
+        <v>45938</v>
+      </c>
+      <c r="C62" s="30">
+        <f>_xll.qlRateHelperMaturityDate(C58)</f>
+        <v>45938</v>
+      </c>
+      <c r="D62" s="22">
+        <f>_xll.qlRateHelperMaturityDate(D58)</f>
+        <v>45938</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B63" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C63" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D63" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D58)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B63" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B58)</f>
+        <v>45938</v>
+      </c>
+      <c r="C63" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(C58)</f>
+        <v>45938</v>
+      </c>
+      <c r="D63" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(D58)</f>
+        <v>45938</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B64" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C64" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C58)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D64" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D58)</f>
-        <v>#NAME?</v>
+      <c r="B64" s="30">
+        <f>_xll.qlRateHelperPillarDate(B58)</f>
+        <v>45938</v>
+      </c>
+      <c r="C64" s="30">
+        <f>_xll.qlRateHelperPillarDate(C58)</f>
+        <v>45938</v>
+      </c>
+      <c r="D64" s="22">
+        <f>_xll.qlRateHelperPillarDate(D58)</f>
+        <v>45846</v>
       </c>
     </row>
   </sheetData>
@@ -4796,14 +5861,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AFCFAD-5375-4B86-AD50-9C25C7C81EAE}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.85546875" customWidth="1"/>
+    <col min="1" max="1" width="45.88671875" customWidth="1"/>
     <col min="2" max="2" width="64" customWidth="1"/>
     <col min="3" max="3" width="69" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -4812,20 +5877,20 @@
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="1" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>116</v>
       </c>
@@ -4836,7 +5901,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>117</v>
       </c>
@@ -4847,7 +5912,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>118</v>
       </c>
@@ -4858,20 +5923,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C7" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C7" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>119</v>
       </c>
@@ -4882,7 +5947,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>120</v>
       </c>
@@ -4893,7 +5958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>121</v>
       </c>
@@ -4904,7 +5969,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>34</v>
       </c>
@@ -4913,7 +5978,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>35</v>
       </c>
@@ -4922,114 +5987,114 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="29" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C13" s="20" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper(C4,C5,C6,C7,C8,C9,C10,,C12)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="29" t="str">
+        <f>_xll.qlFuturesRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R13C2FuturesRateHelper,A</v>
+      </c>
+      <c r="C13" s="20" t="str">
+        <f>_xll.qlFuturesRateHelper(C4,C5,C6,C7,C8,C9,C10,,C12)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R13C3FuturesRateHelper,A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C14" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="31">
+        <f>_xll.qlRateHelperQuote(B13)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C14" s="24">
+        <f>_xll.qlRateHelperQuote(C13)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C15" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="30">
+        <f>_xll.qlRateHelperLatestDate(B13)</f>
+        <v>45918</v>
+      </c>
+      <c r="C15" s="22">
+        <f>_xll.qlRateHelperLatestDate(C13)</f>
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C16" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B13)</f>
+        <v>45826</v>
+      </c>
+      <c r="C16" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C13)</f>
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C17" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B13)</f>
+        <v>45918</v>
+      </c>
+      <c r="C17" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C13)</f>
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C18" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B13)</f>
+        <v>45918</v>
+      </c>
+      <c r="C18" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C13)</f>
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C19" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="30">
+        <f>_xll.qlRateHelperPillarDate(B13)</f>
+        <v>45918</v>
+      </c>
+      <c r="C19" s="22">
+        <f>_xll.qlRateHelperPillarDate(C13)</f>
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="29" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(B13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="20" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(C13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="29">
+        <f>_xll.qlFuturesRateConvexityAdjustment(B13)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="20">
+        <f>_xll.qlFuturesRateConvexityAdjustment(C13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
         <v>116</v>
       </c>
@@ -5040,7 +6105,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="33" t="s">
         <v>117</v>
       </c>
@@ -5051,7 +6116,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>123</v>
       </c>
@@ -5062,7 +6127,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>121</v>
       </c>
@@ -5073,7 +6138,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>122</v>
       </c>
@@ -5082,7 +6147,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>35</v>
       </c>
@@ -5091,111 +6156,111 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="34" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper2(B22,B23,B24,B25)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C28" s="35" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper2(C22,C23,C24,C25,,C27)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="34" t="str">
+        <f>_xll.qlFuturesRateHelper2(B22,B23,B24,B25)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R28C2FuturesRateHelper,A</v>
+      </c>
+      <c r="C28" s="35" t="str">
+        <f>_xll.qlFuturesRateHelper2(C22,C23,C24,C25,,C27)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R28C3FuturesRateHelper,A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C29" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="31">
+        <f>_xll.qlRateHelperQuote(B28)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C29" s="24">
+        <f>_xll.qlRateHelperQuote(C28)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C30" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="30">
+        <f>_xll.qlRateHelperLatestDate(B28)</f>
+        <v>45917</v>
+      </c>
+      <c r="C30" s="22">
+        <f>_xll.qlRateHelperLatestDate(C28)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C31" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B28)</f>
+        <v>45826</v>
+      </c>
+      <c r="C31" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C28)</f>
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C32" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B28)</f>
+        <v>45917</v>
+      </c>
+      <c r="C32" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C28)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C33" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B28)</f>
+        <v>45917</v>
+      </c>
+      <c r="C33" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C28)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C34" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="30">
+        <f>_xll.qlRateHelperPillarDate(B28)</f>
+        <v>45917</v>
+      </c>
+      <c r="C34" s="22">
+        <f>_xll.qlRateHelperPillarDate(C28)</f>
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="29" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(B28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C35" s="20" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(C28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="29">
+        <f>_xll.qlFuturesRateConvexityAdjustment(B28)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="20">
+        <f>_xll.qlFuturesRateConvexityAdjustment(C28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
         <v>116</v>
       </c>
@@ -5206,7 +6271,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>117</v>
       </c>
@@ -5217,20 +6282,20 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="B39" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C39" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("6M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="31" t="str">
+        <f>_xll.qlEuribor("6M")</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R39C2Euribor,A</v>
+      </c>
+      <c r="C39" s="24" t="str">
+        <f>_xll.qlEuribor("6M")</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R39C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>122</v>
       </c>
@@ -5239,7 +6304,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>35</v>
       </c>
@@ -5248,108 +6313,108 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="34" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper3(B37,B38,B39)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C42" s="35" t="e">
-        <f ca="1">_xll.qlFuturesRateHelper3(C37,C38,C39,,C41)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="34" t="str">
+        <f>_xll.qlFuturesRateHelper3(B37,B38,B39)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R42C2FuturesRateHelper,A</v>
+      </c>
+      <c r="C42" s="35" t="str">
+        <f>_xll.qlFuturesRateHelper3(C37,C38,C39,,C41)</f>
+        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R42C3FuturesRateHelper,A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B42)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C43" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C42)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="31">
+        <f>_xll.qlRateHelperQuote(B42)</f>
+        <v>95.5</v>
+      </c>
+      <c r="C43" s="24">
+        <f>_xll.qlRateHelperQuote(C42)</f>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B42)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C44" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C42)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="30">
+        <f>_xll.qlRateHelperLatestDate(B42)</f>
+        <v>46009</v>
+      </c>
+      <c r="C44" s="22">
+        <f>_xll.qlRateHelperLatestDate(C42)</f>
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B42)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C45" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C42)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B42)</f>
+        <v>45826</v>
+      </c>
+      <c r="C45" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C42)</f>
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B42)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C46" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C42)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B42)</f>
+        <v>46009</v>
+      </c>
+      <c r="C46" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C42)</f>
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B47" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B42)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C47" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C42)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B42)</f>
+        <v>46009</v>
+      </c>
+      <c r="C47" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C42)</f>
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B42)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C48" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C42)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="30">
+        <f>_xll.qlRateHelperPillarDate(B42)</f>
+        <v>46009</v>
+      </c>
+      <c r="C48" s="22">
+        <f>_xll.qlRateHelperPillarDate(C42)</f>
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="29" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(B42)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C49" s="20" t="e">
-        <f ca="1">_xll.qlFuturesRateConvexityAdjustment(C42)</f>
-        <v>#NAME?</v>
+      <c r="B49" s="29">
+        <f>_xll.qlFuturesRateConvexityAdjustment(B42)</f>
+        <v>0</v>
+      </c>
+      <c r="C49" s="20">
+        <f>_xll.qlFuturesRateConvexityAdjustment(C42)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5359,15 +6424,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F658185D-C335-4A5F-955B-EF5C79D6BAD3}">
-  <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F63"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.140625" customWidth="1"/>
-    <col min="2" max="2" width="65.140625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="45.109375" customWidth="1"/>
+    <col min="2" max="2" width="65.109375" style="8" customWidth="1"/>
     <col min="3" max="4" width="71" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -5375,23 +6440,23 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>125</v>
       </c>
@@ -5407,7 +6472,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>126</v>
       </c>
@@ -5423,26 +6488,26 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C6" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D6" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
+      <c r="B6" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C6" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D6" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>127</v>
       </c>
@@ -5458,7 +6523,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>128</v>
       </c>
@@ -5474,7 +6539,7 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>129</v>
       </c>
@@ -5490,26 +6555,26 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="B10" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C10" s="31" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D10" s="24" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
+      <c r="B10" s="31" t="str">
+        <f>_xll.qlEuribor("3M",,$B$2)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R10C2Euribor,A</v>
+      </c>
+      <c r="C10" s="31" t="str">
+        <f>_xll.qlEuribor("3M",,$B$2)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R10C3Euribor,A</v>
+      </c>
+      <c r="D10" s="31" t="str">
+        <f>_xll.qlEuribor("3M",,$B$2)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R10C4Euribor,A</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>45</v>
       </c>
@@ -5523,7 +6588,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>130</v>
       </c>
@@ -5537,23 +6602,23 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>153</v>
       </c>
       <c r="B13" s="28"/>
-      <c r="C13" s="28" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D13" s="17" t="e">
-        <f ca="1">_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
+      <c r="C13" s="28" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R13C3YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D13" s="17" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual",B2)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R13C4YieldTermStructureHandle,A</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>47</v>
       </c>
@@ -5567,7 +6632,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>37</v>
       </c>
@@ -5581,7 +6646,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>38</v>
       </c>
@@ -5593,7 +6658,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>2</v>
       </c>
@@ -5607,7 +6672,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>48</v>
       </c>
@@ -5621,417 +6686,419 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="29" t="e">
-        <f ca="1">_xll.qlSwapRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C19" s="29" t="e">
-        <f ca="1">_xll.qlSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,,C17,C18)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D19" s="20" t="e">
-        <f ca="1">_xll.qlSwapRateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="B20" s="29" t="str">
+        <f>_xll.qlSwapRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R20C2SwapRateHelper,A</v>
+      </c>
+      <c r="C20" s="29" t="str">
+        <f>_xll.qlSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,,C17,C18,C19)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R20C3SwapRateHelper,A</v>
+      </c>
+      <c r="D20" s="20" t="str">
+        <f>_xll.qlSwapRateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18,D19)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R20C4SwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D20" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="B21" s="31">
+        <f>_xll.qlRateHelperQuote(B20)</f>
+        <v>0.04</v>
+      </c>
+      <c r="C21" s="31">
+        <f>_xll.qlRateHelperQuote(C20)</f>
+        <v>0.04</v>
+      </c>
+      <c r="D21" s="24">
+        <f>_xll.qlRateHelperQuote(D20)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C21" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D21" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="B22" s="30">
+        <f>_xll.qlRateHelperLatestDate(B20)</f>
+        <v>45755</v>
+      </c>
+      <c r="C22" s="30">
+        <f>_xll.qlRateHelperLatestDate(C20)</f>
+        <v>45846</v>
+      </c>
+      <c r="D22" s="22">
+        <f>_xll.qlRateHelperLatestDate(D20)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C22" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D22" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="B23" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B20)</f>
+        <v>45665</v>
+      </c>
+      <c r="C23" s="28">
+        <f>_xll.qlRateHelperEarliestDate(C20)</f>
+        <v>45755</v>
+      </c>
+      <c r="D23" s="17">
+        <f>_xll.qlRateHelperEarliestDate(D20)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C23" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D23" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="B24" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B20)</f>
+        <v>45755</v>
+      </c>
+      <c r="C24" s="30">
+        <f>_xll.qlRateHelperMaturityDate(C20)</f>
+        <v>45846</v>
+      </c>
+      <c r="D24" s="22">
+        <f>_xll.qlRateHelperMaturityDate(D20)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C24" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D24" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="B25" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B20)</f>
+        <v>45755</v>
+      </c>
+      <c r="C25" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(C20)</f>
+        <v>45846</v>
+      </c>
+      <c r="D25" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(D20)</f>
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C25" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D25" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="40" t="s">
+      <c r="B26" s="30">
+        <f>_xll.qlRateHelperPillarDate(B20)</f>
+        <v>45755</v>
+      </c>
+      <c r="C26" s="30">
+        <f>_xll.qlRateHelperPillarDate(C20)</f>
+        <v>45846</v>
+      </c>
+      <c r="D26" s="22">
+        <f>_xll.qlRateHelperPillarDate(D20)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="31" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C26" s="31" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(C19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D26" s="24" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(D19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
+      <c r="B27" s="31">
+        <f>_xll.qlSwapRateHelperSpread(B20)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="31">
+        <f>_xll.qlSwapRateHelperSpread(C20)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="24">
+        <f>_xll.qlSwapRateHelperSpread(D20)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="38" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(B19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C27" s="38" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(C19)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D27" s="39" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(D19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
+      <c r="B28" s="38" t="str">
+        <f>_xll.qlSwapRateHelperSwap(B20)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R28C2VanillaSwap,A</v>
+      </c>
+      <c r="C28" s="38" t="str">
+        <f>_xll.qlSwapRateHelperSwap(C20)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R28C3VanillaSwap,A</v>
+      </c>
+      <c r="D28" s="39" t="str">
+        <f>_xll.qlSwapRateHelperSwap(D20)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R28C4VanillaSwap,A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B30" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C30" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="43" t="s">
+      <c r="D30" s="43" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="45" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="45" t="s">
+      <c r="C31" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="46" t="s">
+      <c r="D31" s="46" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="45">
+      <c r="B32" s="45">
         <v>2</v>
       </c>
-      <c r="C31" s="45">
+      <c r="C32" s="45">
         <v>2</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D32" s="46">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="44" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B33" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="C33" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D33" s="46" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="44" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="45" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C33" s="45" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D33" s="46" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="44" t="s">
+      <c r="B34" s="45" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C34" s="45" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D34" s="46" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="45" t="s">
+      <c r="B35" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="45" t="s">
+      <c r="C35" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D34" s="46" t="s">
+      <c r="D35" s="46" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="44" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="45" t="s">
+      <c r="B36" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="45" t="s">
+      <c r="C36" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="46" t="s">
+      <c r="D36" s="46" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="44" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="45" t="s">
+      <c r="B37" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="45" t="s">
+      <c r="C37" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D37" s="46" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="44" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="45" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C37" s="45" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D37" s="46" t="e">
-        <f ca="1">_xll.qlEuribor("3M")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="44" t="s">
+      <c r="B38" s="45" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R38C2Euribor,A</v>
+      </c>
+      <c r="C38" s="45" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R38C3Euribor,A</v>
+      </c>
+      <c r="D38" s="46" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R38C4Euribor,A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="45" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C38" s="45" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D38" s="46" t="e">
-        <f ca="1">_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="47" t="s">
+      <c r="B39" s="45" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R39C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C39" s="45" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R39C3YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D39" s="46" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R39C4YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="48">
+      <c r="B40" s="48">
         <v>0.04</v>
       </c>
-      <c r="C39" s="48">
+      <c r="C40" s="48">
         <v>0.04</v>
       </c>
-      <c r="D39" s="49">
+      <c r="D40" s="49">
         <v>0.04</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="47" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="31" t="e">
-        <f ca="1">_xll.qlSwapIndex(B29,B30,B31,B32,B33,B34,B35,B36,B37,B38)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C40" s="31" t="e">
-        <f ca="1">_xll.qlSwapIndex(C29,C30,C31,C32,C33,C34,C35,C36,C37,C38)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D40" s="24" t="e">
-        <f ca="1">_xll.qlSwapIndex(D29,D30,D31,D32,D33,D34,D35,D36,D37,D38)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="47" t="s">
+      <c r="B41" s="31" t="str">
+        <f>_xll.qlSwapIndex(B30,B31,B32,B33,B34,B35,B36,B37,B38,B39)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R41C2SwapIndex,A</v>
+      </c>
+      <c r="C41" s="31" t="str">
+        <f>_xll.qlSwapIndex(C30,C31,C32,C33,C34,C35,C36,C37,C38,C39)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R41C3SwapIndex,A</v>
+      </c>
+      <c r="D41" s="24" t="str">
+        <f>_xll.qlSwapIndex(D30,D31,D32,D33,D34,D35,D36,D37,D38,D39)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R41C4SwapIndex,A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31">
+      <c r="B42" s="31"/>
+      <c r="C42" s="31">
         <v>0.6</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D42" s="24">
         <v>0.6</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="47" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31" t="s">
+      <c r="B43" s="31"/>
+      <c r="C43" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D43" s="24" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="47" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D43" s="24" t="e">
-        <f ca="1">_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="47" t="s">
+      <c r="B44" s="31"/>
+      <c r="C44" s="31" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R44C3YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D44" s="24" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R44C4YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31" t="s">
+      <c r="B45" s="31"/>
+      <c r="C45" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D45" s="17" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="47" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="17">
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="17">
         <v>45784</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="47" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="47" t="s">
         <v>120</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31">
-        <v>1</v>
-      </c>
-      <c r="D46" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="47" t="s">
-        <v>48</v>
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="31">
@@ -6041,164 +7108,176 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31">
+        <v>1</v>
+      </c>
+      <c r="D48" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="29" t="e">
-        <f ca="1">_xll.qlSwapRateHelper2(B39,B40)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C48" s="29" t="e">
-        <f ca="1">_xll.qlSwapRateHelper2(C39,C40,C41,C42,C43,C44,,C46,C47)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D48" s="20" t="e">
-        <f ca="1">_xll.qlSwapRateHelper2(D39,D40,D41,D42,D43,D44,D45,D46,D47)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="s">
+      <c r="B49" s="29" t="str">
+        <f>_xll.qlSwapRateHelper2(B40,B41)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R49C2SwapRateHelper,A</v>
+      </c>
+      <c r="C49" s="29" t="str">
+        <f>_xll.qlSwapRateHelper2(C40,C41,C42,C43,C44,C45,,C47,C48)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R49C3SwapRateHelper,A</v>
+      </c>
+      <c r="D49" s="20" t="str">
+        <f>_xll.qlSwapRateHelper2(D40,D41,D42,D43,D44,D45,D46,D47,D48)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R49C4SwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B49" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C49" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D49" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D48)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="B50" s="31">
+        <f>_xll.qlRateHelperQuote(B49)</f>
+        <v>0.04</v>
+      </c>
+      <c r="C50" s="31">
+        <f>_xll.qlRateHelperQuote(C49)</f>
+        <v>0.04</v>
+      </c>
+      <c r="D50" s="24">
+        <f>_xll.qlRateHelperQuote(D49)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C50" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D50" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D48)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="23" t="s">
+      <c r="B51" s="30">
+        <f>_xll.qlRateHelperLatestDate(B49)</f>
+        <v>45755</v>
+      </c>
+      <c r="C51" s="30">
+        <f>_xll.qlRateHelperLatestDate(C49)</f>
+        <v>45789</v>
+      </c>
+      <c r="D51" s="22">
+        <f>_xll.qlRateHelperLatestDate(D49)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C51" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D51" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D48)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="B52" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B49)</f>
+        <v>45665</v>
+      </c>
+      <c r="C52" s="28">
+        <f>_xll.qlRateHelperEarliestDate(C49)</f>
+        <v>45698</v>
+      </c>
+      <c r="D52" s="17">
+        <f>_xll.qlRateHelperEarliestDate(D49)</f>
+        <v>45698</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C52" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D52" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D48)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="23" t="s">
+      <c r="B53" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B49)</f>
+        <v>45755</v>
+      </c>
+      <c r="C53" s="30">
+        <f>_xll.qlRateHelperMaturityDate(C49)</f>
+        <v>45789</v>
+      </c>
+      <c r="D53" s="22">
+        <f>_xll.qlRateHelperMaturityDate(D49)</f>
+        <v>45789</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B53" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C53" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D53" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D48)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
+      <c r="B54" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B49)</f>
+        <v>45755</v>
+      </c>
+      <c r="C54" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(C49)</f>
+        <v>45789</v>
+      </c>
+      <c r="D54" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(D49)</f>
+        <v>45789</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B54" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C54" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D54" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D48)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="40" t="s">
+      <c r="B55" s="30">
+        <f>_xll.qlRateHelperPillarDate(B49)</f>
+        <v>45755</v>
+      </c>
+      <c r="C55" s="30">
+        <f>_xll.qlRateHelperPillarDate(C49)</f>
+        <v>45789</v>
+      </c>
+      <c r="D55" s="22">
+        <f>_xll.qlRateHelperPillarDate(D49)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="31" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(B48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C55" s="31" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(C48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D55" s="24" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSpread(D48)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="37" t="s">
+      <c r="B56" s="31">
+        <f>_xll.qlSwapRateHelperSpread(B49)</f>
+        <v>0</v>
+      </c>
+      <c r="C56" s="31">
+        <f>_xll.qlSwapRateHelperSpread(C49)</f>
+        <v>0.6</v>
+      </c>
+      <c r="D56" s="24">
+        <f>_xll.qlSwapRateHelperSpread(D49)</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="38" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(B48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C56" s="38" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(C48)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D56" s="39" t="e">
-        <f ca="1">_xll.qlSwapRateHelperSwap(D48)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B61" s="7"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="38" t="str">
+        <f>_xll.qlSwapRateHelperSwap(B49)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R57C2VanillaSwap,A</v>
+      </c>
+      <c r="C57" s="38" t="str">
+        <f>_xll.qlSwapRateHelperSwap(C49)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R57C3VanillaSwap,A</v>
+      </c>
+      <c r="D57" s="39" t="str">
+        <f>_xll.qlSwapRateHelperSwap(D49)</f>
+        <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R57C4VanillaSwap,A</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62" s="7"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B63" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -6209,14 +7288,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59EEA4C7-BB60-4D88-9707-F3D141976843}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -6224,16 +7303,16 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="61" t="s">
         <v>212</v>
       </c>
@@ -6244,7 +7323,7 @@
         <v>101.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>47</v>
       </c>
@@ -6255,7 +7334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>201</v>
       </c>
@@ -6266,7 +7345,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="62" t="s">
         <v>206</v>
       </c>
@@ -6277,7 +7356,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="59" t="s">
         <v>207</v>
       </c>
@@ -6288,7 +7367,7 @@
         <v>47120</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="59" t="s">
         <v>0</v>
       </c>
@@ -6299,7 +7378,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="59" t="s">
         <v>21</v>
       </c>
@@ -6310,7 +7389,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="59" t="s">
         <v>81</v>
       </c>
@@ -6321,7 +7400,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="59" t="s">
         <v>208</v>
       </c>
@@ -6332,7 +7411,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="59" t="s">
         <v>209</v>
       </c>
@@ -6343,7 +7422,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="59" t="s">
         <v>2</v>
       </c>
@@ -6354,20 +7433,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="65" t="s">
         <v>202</v>
       </c>
-      <c r="B15" s="29" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlSchedule(B7,B8,B9,B10,B11,B12,B13,B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C15" s="20" t="e" cm="1">
-        <f t="array" aca="1" ref="C15" ca="1">_xll.qlSchedule(C7,C8,C9,C10,C11,C12,C13,C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="29" t="str" cm="1">
+        <f t="array" ref="B15">_xll.qlSchedule(B7,B8,B9,B10,B11,B12,B13,B14)</f>
+        <v>欣[test_ratehelpers.xlsx]BondHelper!R15C2Schedule,A</v>
+      </c>
+      <c r="C15" s="20" t="str" cm="1">
+        <f t="array" ref="C15">_xll.qlSchedule(C7,C8,C9,C10,C11,C12,C13,C14)</f>
+        <v>欣[test_ratehelpers.xlsx]BondHelper!R15C3Schedule,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>205</v>
       </c>
@@ -6378,7 +7457,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>203</v>
       </c>
@@ -6389,20 +7468,20 @@
         <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="B18" s="29" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlFixedRateBond(B5,B6,B15,B16,B17)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C18" s="20" t="e" cm="1">
-        <f t="array" aca="1" ref="C18" ca="1">_xll.qlFixedRateBond(C5,C6,C15,C16,C17)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="29" t="str" cm="1">
+        <f t="array" ref="B18">_xll.qlFixedRateBond(B5,B6,B15,B16,B17)</f>
+        <v>欣[test_ratehelpers.xlsx]BondHelper!R18C2FixedRateBond,A</v>
+      </c>
+      <c r="C18" s="20" t="str" cm="1">
+        <f t="array" ref="C18">_xll.qlFixedRateBond(C5,C6,C15,C16,C17)</f>
+        <v>欣[test_ratehelpers.xlsx]BondHelper!R18C3FixedRateBond,A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="66" t="s">
         <v>213</v>
       </c>
@@ -6411,95 +7490,95 @@
         <v>214</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="67" t="s">
         <v>215</v>
       </c>
-      <c r="B20" s="29" t="e" cm="1">
-        <f t="array" aca="1" ref="B20" ca="1">_xll.qlBondHelper(B4,B18)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="20" t="e" cm="1">
-        <f t="array" aca="1" ref="C20" ca="1">_xll.qlBondHelper(C4,C18,C19)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="29" t="str" cm="1">
+        <f t="array" ref="B20">_xll.qlBondHelper(B4,B18)</f>
+        <v>欣[test_ratehelpers.xlsx]BondHelper!R20C2BondHelper,A</v>
+      </c>
+      <c r="C20" s="20" t="str" cm="1">
+        <f t="array" ref="C20">_xll.qlBondHelper(C4,C18,C19)</f>
+        <v>欣[test_ratehelpers.xlsx]BondHelper!R20C3BondHelper,A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C21" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C20)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="31">
+        <f>_xll.qlRateHelperQuote(B20)</f>
+        <v>101.5</v>
+      </c>
+      <c r="C21" s="24">
+        <f>_xll.qlRateHelperQuote(C20)</f>
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C22" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C20)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="30">
+        <f>_xll.qlRateHelperLatestDate(B20)</f>
+        <v>47120</v>
+      </c>
+      <c r="C22" s="22">
+        <f>_xll.qlRateHelperLatestDate(C20)</f>
+        <v>47120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C23" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C20)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B20)</f>
+        <v>45840</v>
+      </c>
+      <c r="C23" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C20)</f>
+        <v>45840</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C24" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C20)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B20)</f>
+        <v>47120</v>
+      </c>
+      <c r="C24" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C20)</f>
+        <v>47120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C25" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C20)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B20)</f>
+        <v>47120</v>
+      </c>
+      <c r="C25" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C20)</f>
+        <v>47120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B20)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C26" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C20)</f>
-        <v>#NAME?</v>
+      <c r="B26" s="30">
+        <f>_xll.qlRateHelperPillarDate(B20)</f>
+        <v>47120</v>
+      </c>
+      <c r="C26" s="22">
+        <f>_xll.qlRateHelperPillarDate(C20)</f>
+        <v>47120</v>
       </c>
     </row>
   </sheetData>
@@ -6513,33 +7592,33 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A2:I7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I7" s="1"/>
     </row>
   </sheetData>
@@ -6550,14 +7629,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8D3E72-38D5-454D-A3CB-8D63AEF54296}">
   <dimension ref="A1:D36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.42578125" customWidth="1"/>
-    <col min="2" max="2" width="66.85546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="44.44140625" customWidth="1"/>
+    <col min="2" max="2" width="66.88671875" style="8" customWidth="1"/>
     <col min="3" max="4" width="76" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -6565,19 +7644,19 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>140</v>
       </c>
@@ -6591,7 +7670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>126</v>
       </c>
@@ -6605,7 +7684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>141</v>
       </c>
@@ -6619,38 +7698,38 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="28" t="e">
-        <f ca="1">_xll.qlSofr()</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C7" s="28" t="e">
-        <f ca="1">_xll.qlSofr()</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D7" s="17" t="e">
-        <f ca="1">_xll.qlSofr()</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="28" t="str">
+        <f>_xll.qlSofr()</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R7C2Sofr,A</v>
+      </c>
+      <c r="C7" s="28" t="str">
+        <f>_xll.qlSofr()</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R7C3Sofr,A</v>
+      </c>
+      <c r="D7" s="17" t="str">
+        <f>_xll.qlSofr()</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R7C4Sofr,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
       <c r="B8" s="28"/>
-      <c r="C8" s="28" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D8" s="17" t="e">
-        <f ca="1">_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="28" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R8C3YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D8" s="17" t="str">
+        <f>_xll.qlFlatForward(C1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R8C4YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>143</v>
       </c>
@@ -6662,7 +7741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>100</v>
       </c>
@@ -6674,7 +7753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>144</v>
       </c>
@@ -6686,7 +7765,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>95</v>
       </c>
@@ -6698,21 +7777,21 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>154</v>
       </c>
       <c r="B13" s="28"/>
-      <c r="C13" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D13" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D13" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>145</v>
       </c>
@@ -6724,7 +7803,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>146</v>
       </c>
@@ -6736,7 +7815,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>134</v>
       </c>
@@ -6748,7 +7827,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>38</v>
       </c>
@@ -6758,7 +7837,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>147</v>
       </c>
@@ -6770,7 +7849,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>120</v>
       </c>
@@ -6782,7 +7861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>53</v>
       </c>
@@ -6794,21 +7873,21 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>156</v>
       </c>
       <c r="B21" s="28"/>
-      <c r="C21" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D21" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D21" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>148</v>
       </c>
@@ -6820,7 +7899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>149</v>
       </c>
@@ -6832,7 +7911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>150</v>
       </c>
@@ -6844,7 +7923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>151</v>
       </c>
@@ -6852,7 +7931,7 @@
       <c r="C25" s="28"/>
       <c r="D25" s="17"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>152</v>
       </c>
@@ -6864,21 +7943,21 @@
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>158</v>
       </c>
       <c r="B27" s="28"/>
-      <c r="C27" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D27" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="D27" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>81</v>
       </c>
@@ -6890,140 +7969,140 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="29" t="e">
-        <f ca="1">_xll.qlOISRateHelper(B4,B5,B6,B7)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C29" s="29" t="e">
-        <f ca="1">_xll.qlOISRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,,C18,C19,C20,C21,C22,C23,C24,,C26,C27,C28)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D29" s="20" t="e">
-        <f ca="1">_xll.qlOISRateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D23,D24,,D26,D27,D28)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="29" t="str">
+        <f>_xll.qlOISRateHelper(B4,B5,B6,B7)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R29C2OISRateHelper,A</v>
+      </c>
+      <c r="C29" s="29" t="str">
+        <f>_xll.qlOISRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,,C18,C19,C20,C21,C22,C23,C24,,C26,C27,C28)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R29C3OISRateHelper,A</v>
+      </c>
+      <c r="D29" s="20" t="str">
+        <f>_xll.qlOISRateHelper(D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D23,D24,,D26,D27,D28)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R29C4OISRateHelper,A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C30" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D30" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="31">
+        <f>_xll.qlRateHelperQuote(B29)</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C30" s="31">
+        <f>_xll.qlRateHelperQuote(C29)</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D30" s="24">
+        <f>_xll.qlRateHelperQuote(D29)</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C31" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D31" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="30">
+        <f>_xll.qlRateHelperLatestDate(B29)</f>
+        <v>45756</v>
+      </c>
+      <c r="C31" s="30">
+        <f>_xll.qlRateHelperLatestDate(C29)</f>
+        <v>45791</v>
+      </c>
+      <c r="D31" s="22">
+        <f>_xll.qlRateHelperLatestDate(D29)</f>
+        <v>45791</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C32" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D32" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B29)</f>
+        <v>45666</v>
+      </c>
+      <c r="C32" s="28">
+        <f>_xll.qlRateHelperEarliestDate(C29)</f>
+        <v>45698</v>
+      </c>
+      <c r="D32" s="17">
+        <f>_xll.qlRateHelperEarliestDate(D29)</f>
+        <v>45698</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C33" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D33" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B29)</f>
+        <v>45756</v>
+      </c>
+      <c r="C33" s="30">
+        <f>_xll.qlRateHelperMaturityDate(C29)</f>
+        <v>45789</v>
+      </c>
+      <c r="D33" s="22">
+        <f>_xll.qlRateHelperMaturityDate(D29)</f>
+        <v>45789</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C34" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D34" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B29)</f>
+        <v>45756</v>
+      </c>
+      <c r="C34" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(C29)</f>
+        <v>45791</v>
+      </c>
+      <c r="D34" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(D29)</f>
+        <v>45791</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C35" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D35" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(D29)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="30">
+        <f>_xll.qlRateHelperPillarDate(B29)</f>
+        <v>45756</v>
+      </c>
+      <c r="C35" s="30">
+        <f>_xll.qlRateHelperPillarDate(C29)</f>
+        <v>45789</v>
+      </c>
+      <c r="D35" s="22">
+        <f>_xll.qlRateHelperPillarDate(D29)</f>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="29" t="e">
-        <f ca="1">_xll.qlOISRateHelperSwap(B29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C36" s="29" t="e">
-        <f ca="1">_xll.qlOISRateHelperSwap(C29)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D36" s="20" t="e">
-        <f ca="1">_xll.qlOISRateHelperSwap(D29)</f>
-        <v>#NAME?</v>
+      <c r="B36" s="29" t="str">
+        <f>_xll.qlOISRateHelperSwap(B29)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R36C2OvernightIndexedSwap,A</v>
+      </c>
+      <c r="C36" s="29" t="str">
+        <f>_xll.qlOISRateHelperSwap(C29)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R36C3OvernightIndexedSwap,A</v>
+      </c>
+      <c r="D36" s="20" t="str">
+        <f>_xll.qlOISRateHelperSwap(D29)</f>
+        <v>欣[test_ratehelpers.xlsx]OISRateHelper!R36C4OvernightIndexedSwap,A</v>
       </c>
     </row>
   </sheetData>
@@ -7035,14 +8114,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C2BEAF-FCDE-48B0-B97E-27F830DD2C98}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" customWidth="1"/>
-    <col min="2" max="2" width="73.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="52.33203125" customWidth="1"/>
+    <col min="2" max="2" width="73.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.33203125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -7050,19 +8129,19 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>66</v>
       </c>
@@ -7073,7 +8152,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>67</v>
       </c>
@@ -7084,7 +8163,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>0</v>
       </c>
@@ -7095,7 +8174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>14</v>
       </c>
@@ -7106,20 +8185,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="28" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C8" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C8" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>22</v>
       </c>
@@ -7130,7 +8209,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>2</v>
       </c>
@@ -7141,7 +8220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>68</v>
       </c>
@@ -7152,232 +8231,232 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="28" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C12" s="17" t="e">
-        <f ca="1">_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="28" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R12C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C12" s="17" t="str">
+        <f>_xll.qlFlatForward(B1,0.03,"Actual360","Compounded","Annual")</f>
+        <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R12C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
       <c r="B13" s="28"/>
-      <c r="C13" s="17" t="e">
-        <f ca="1">_xll.qlCalendar("TARGET")</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="17" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="29" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C14" s="20" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="29" t="str">
+        <f>_xll.qlFxSwapRateHelper(B4,B5,B6,B7,B8,B9,B10,B11,B12)</f>
+        <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R14C2FxSwapRateHelper,A</v>
+      </c>
+      <c r="C14" s="20" t="str">
+        <f>_xll.qlFxSwapRateHelper(C4,C5,C6,C7,C8,C9,C10,C11,C12,C13)</f>
+        <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R14C3FxSwapRateHelper,A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="31" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C15" s="24" t="e">
-        <f ca="1">_xll.qlRateHelperQuote(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="31">
+        <f>_xll.qlRateHelperQuote(B14)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C15" s="24">
+        <f>_xll.qlRateHelperQuote(C14)</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C16" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperLatestDate(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="30">
+        <f>_xll.qlRateHelperLatestDate(B14)</f>
+        <v>45755</v>
+      </c>
+      <c r="C16" s="22">
+        <f>_xll.qlRateHelperLatestDate(C14)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C17" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperEarliestDate(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="28">
+        <f>_xll.qlRateHelperEarliestDate(B14)</f>
+        <v>45665</v>
+      </c>
+      <c r="C17" s="17">
+        <f>_xll.qlRateHelperEarliestDate(C14)</f>
+        <v>45664</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C18" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperMaturityDate(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="30">
+        <f>_xll.qlRateHelperMaturityDate(B14)</f>
+        <v>45755</v>
+      </c>
+      <c r="C18" s="22">
+        <f>_xll.qlRateHelperMaturityDate(C14)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="28" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C19" s="17" t="e">
-        <f ca="1">_xll.qlRateHelperLatestRelevantDate(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="28">
+        <f>_xll.qlRateHelperLatestRelevantDate(B14)</f>
+        <v>45755</v>
+      </c>
+      <c r="C19" s="17">
+        <f>_xll.qlRateHelperLatestRelevantDate(C14)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="30" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C20" s="22" t="e">
-        <f ca="1">_xll.qlRateHelperPillarDate(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="30">
+        <f>_xll.qlRateHelperPillarDate(B14)</f>
+        <v>45755</v>
+      </c>
+      <c r="C20" s="22">
+        <f>_xll.qlRateHelperPillarDate(C14)</f>
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="31" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperSpot(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C21" s="24" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperSpot(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="31">
+        <f>_xll.qlFxSwapRateHelperSpot(B14)</f>
+        <v>0.97</v>
+      </c>
+      <c r="C21" s="24">
+        <f>_xll.qlFxSwapRateHelperSpot(C14)</f>
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="38" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperTenor(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C22" s="39" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperTenor(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="38" t="str">
+        <f>_xll.qlFxSwapRateHelperTenor(B14)</f>
+        <v>3M</v>
+      </c>
+      <c r="C22" s="39" t="str">
+        <f>_xll.qlFxSwapRateHelperTenor(C14)</f>
+        <v>3M</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="31" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperFixingDays(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C23" s="24" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperFixingDays(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="31">
+        <f>_xll.qlFxSwapRateHelperFixingDays(B14)</f>
+        <v>2</v>
+      </c>
+      <c r="C23" s="24">
+        <f>_xll.qlFxSwapRateHelperFixingDays(C14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="38" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperCalendar(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C24" s="39" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperCalendar(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="38" t="str">
+        <f>_xll.qlFxSwapRateHelperCalendar(B14)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C24" s="39" t="str">
+        <f>_xll.qlFxSwapRateHelperCalendar(C14)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="54" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperBusinessDayConvention(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C25" s="55" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperBusinessDayConvention(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="54">
+        <f>_xll.qlFxSwapRateHelperBusinessDayConvention(B14)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="55">
+        <f>_xll.qlFxSwapRateHelperBusinessDayConvention(C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="38" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperEndOfMonth(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C26" s="39" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperEndOfMonth(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="38" t="b">
+        <f>_xll.qlFxSwapRateHelperEndOfMonth(B14)</f>
+        <v>1</v>
+      </c>
+      <c r="C26" s="39" t="b">
+        <f>_xll.qlFxSwapRateHelperEndOfMonth(C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="31" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperIsFxBaseCurrencyCollateralCurrency(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C27" s="24" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperIsFxBaseCurrencyCollateralCurrency(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="31" t="b">
+        <f>_xll.qlFxSwapRateHelperIsFxBaseCurrencyCollateralCurrency(B14)</f>
+        <v>1</v>
+      </c>
+      <c r="C27" s="24" t="b">
+        <f>_xll.qlFxSwapRateHelperIsFxBaseCurrencyCollateralCurrency(C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
         <v>77</v>
       </c>
       <c r="B28" s="38"/>
-      <c r="C28" s="39" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperTradingCalendar(C14)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="39" t="str">
+        <f>_xll.qlFxSwapRateHelperTradingCalendar(C14)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="29" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperAdjustmentCalendar(B14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C29" s="20" t="e">
-        <f ca="1">_xll.qlFxSwapRateHelperAdjustmentCalendar(C14)</f>
-        <v>#NAME?</v>
+      <c r="B29" s="29" t="str">
+        <f>_xll.qlFxSwapRateHelperAdjustmentCalendar(B14)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C29" s="20" t="str">
+        <f>_xll.qlFxSwapRateHelperAdjustmentCalendar(C14)</f>
+        <v>JoinHolidays(TARGET, TARGET)</v>
       </c>
     </row>
   </sheetData>
